--- a/ResourcesPK/OutletExcel.xlsx
+++ b/ResourcesPK/OutletExcel.xlsx
@@ -14,12 +14,12 @@
   <sheets>
     <sheet name="Excel Template" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" concurrentManualCount="8"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="64">
   <si>
     <t>Distributor*</t>
   </si>
@@ -208,6 +208,9 @@
   </si>
   <si>
     <t>03076308091</t>
+  </si>
+  <si>
+    <t>Advance Tax Exemption</t>
   </si>
 </sst>
 </file>
@@ -531,7 +534,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A1:AF3"/>
   <sheetFormatPr defaultColWidth="8.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.81640625" style="1" bestFit="1" customWidth="1"/>
@@ -564,9 +567,10 @@
     <col min="29" max="29" width="13.36328125" bestFit="1" customWidth="1"/>
     <col min="30" max="30" width="10.54296875" bestFit="1" customWidth="1"/>
     <col min="31" max="31" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="20.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -660,8 +664,11 @@
       <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
+      <c r="AF1" t="s">
+        <v>63</v>
+      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>31</v>
       </c>
@@ -755,8 +762,11 @@
       <c r="AE2" s="2">
         <v>10</v>
       </c>
+      <c r="AF2" t="s">
+        <v>51</v>
+      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>31</v>
       </c>
@@ -849,6 +859,9 @@
       </c>
       <c r="AE3" s="2">
         <v>30</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>51</v>
       </c>
     </row>
   </sheetData>

--- a/ResourcesPK/OutletExcel.xlsx
+++ b/ResourcesPK/OutletExcel.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="164011"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Automation\ExcelGenerator\ResourcesPK\"/>
     </mc:Choice>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="106">
   <si>
     <t>Distributor*</t>
   </si>
@@ -211,6 +211,132 @@
   </si>
   <si>
     <t>Advance Tax Exemption</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL21B5F</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3B74A</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLAAA08</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB909D</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDBF87</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC7EA1</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL3AE2B</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLBE84F</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL8B5F1</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLA05F1</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL00A5E</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2EA24</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB41A3</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLACCAF</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLCD449</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL6DC73</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL91514</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL37C05</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC6424</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL825EE</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC00F6</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL62FA0</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLBB490</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL9ABBB</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF215C</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL67B50</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL4239B</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLDFE4D</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLF1A62</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL14478</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL13179</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLB8139</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL0109F</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL44906</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL00DC0</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLAE044</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL2AB0C</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL89617</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL003B4</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLC8DB6</t>
+  </si>
+  <si>
+    <t>AUTO_OUTL9A5B6</t>
+  </si>
+  <si>
+    <t>AUTO_OUTLD07B2</t>
   </si>
 </sst>
 </file>
@@ -537,37 +663,37 @@
   <dimension ref="A1:AF3"/>
   <sheetFormatPr defaultColWidth="8.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="23.6328125" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="6.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.1796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="15" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="6.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="20.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="13.08984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.453125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="22.90625" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="15" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="26.36328125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="8" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="4.81640625" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14" style="2" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="17.6328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.1796875" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.36328125" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="10.54296875" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="20.1796875" customWidth="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="10.81640625"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="11.90625"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="18.90625"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="12.1796875"/>
+    <col min="5" max="6" bestFit="true" customWidth="true" style="3" width="23.6328125"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" width="6.90625"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="10.1796875"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="10" max="10" bestFit="true" customWidth="true" width="14.0"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.453125"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="6.08984375"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="13.54296875"/>
+    <col min="14" max="14" bestFit="true" customWidth="true" style="1" width="20.08984375"/>
+    <col min="15" max="15" bestFit="true" customWidth="true" style="1" width="16.08984375"/>
+    <col min="16" max="16" bestFit="true" customWidth="true" style="1" width="18.453125"/>
+    <col min="17" max="17" bestFit="true" customWidth="true" style="1" width="13.08984375"/>
+    <col min="18" max="18" bestFit="true" customWidth="true" style="1" width="20.453125"/>
+    <col min="19" max="19" bestFit="true" customWidth="true" style="1" width="12.0"/>
+    <col min="20" max="20" bestFit="true" customWidth="true" style="1" width="22.90625"/>
+    <col min="21" max="21" bestFit="true" customWidth="true" width="15.0"/>
+    <col min="22" max="22" bestFit="true" customWidth="true" width="26.36328125"/>
+    <col min="23" max="23" bestFit="true" customWidth="true" width="8.0"/>
+    <col min="24" max="24" bestFit="true" customWidth="true" width="4.81640625"/>
+    <col min="25" max="25" bestFit="true" customWidth="true" style="1" width="14.0"/>
+    <col min="26" max="26" bestFit="true" customWidth="true" style="2" width="14.0"/>
+    <col min="27" max="27" bestFit="true" customWidth="true" style="2" width="17.6328125"/>
+    <col min="28" max="28" bestFit="true" customWidth="true" width="14.1796875"/>
+    <col min="29" max="29" bestFit="true" customWidth="true" width="13.36328125"/>
+    <col min="30" max="30" bestFit="true" customWidth="true" width="10.54296875"/>
+    <col min="31" max="31" bestFit="true" customWidth="true" style="2" width="16.7265625"/>
+    <col min="32" max="32" customWidth="true" width="20.1796875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.35">
@@ -589,16 +715,16 @@
       <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" t="s" s="0">
         <v>6</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" t="s" s="0">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" t="s" s="0">
         <v>9</v>
       </c>
       <c r="K1" s="1" t="s">
@@ -631,16 +757,16 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="U1" t="s">
+      <c r="U1" t="s" s="0">
         <v>20</v>
       </c>
-      <c r="V1" t="s">
+      <c r="V1" t="s" s="0">
         <v>21</v>
       </c>
-      <c r="W1" t="s">
+      <c r="W1" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="X1" t="s">
+      <c r="X1" t="s" s="0">
         <v>23</v>
       </c>
       <c r="Y1" s="1" t="s">
@@ -652,19 +778,19 @@
       <c r="AA1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AB1" t="s" s="0">
         <v>27</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AC1" t="s" s="0">
         <v>28</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AD1" t="s" s="0">
         <v>29</v>
       </c>
       <c r="AE1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AF1" t="s" s="0">
         <v>63</v>
       </c>
     </row>
@@ -676,7 +802,7 @@
         <v>32</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>33</v>
+        <v>104</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>34</v>
@@ -687,16 +813,16 @@
       <c r="F2" s="3">
         <v>44.456310000000002</v>
       </c>
-      <c r="G2" t="s">
+      <c r="G2" t="s" s="0">
         <v>35</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" t="s" s="0">
         <v>38</v>
       </c>
       <c r="K2" s="1" t="s">
@@ -729,16 +855,16 @@
       <c r="T2" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="U2" t="s">
+      <c r="U2" t="s" s="0">
         <v>49</v>
       </c>
-      <c r="V2" t="s">
+      <c r="V2" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="W2" t="s">
+      <c r="W2" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="X2" t="s">
+      <c r="X2" t="s" s="0">
         <v>50</v>
       </c>
       <c r="Y2" s="1" t="s">
@@ -750,19 +876,19 @@
       <c r="AA2" s="2">
         <v>300000</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AB2" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AC2" t="s" s="0">
         <v>52</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AD2" t="s" s="0">
         <v>52</v>
       </c>
       <c r="AE2" s="2">
         <v>10</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AF2" t="s" s="0">
         <v>51</v>
       </c>
     </row>
@@ -774,7 +900,7 @@
         <v>53</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>54</v>
+        <v>105</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>34</v>
@@ -785,16 +911,16 @@
       <c r="F3" s="3">
         <v>10.32</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" t="s" s="0">
         <v>35</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="I3" t="s">
+      <c r="I3" t="s" s="0">
         <v>51</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" t="s" s="0">
         <v>52</v>
       </c>
       <c r="K3" s="1" t="s">
@@ -827,16 +953,16 @@
       <c r="T3" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="U3" t="s">
+      <c r="U3" t="s" s="0">
         <v>62</v>
       </c>
-      <c r="V3" t="s">
+      <c r="V3" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="W3" t="s">
+      <c r="W3" t="s" s="0">
         <v>50</v>
       </c>
-      <c r="X3" t="s">
+      <c r="X3" t="s" s="0">
         <v>50</v>
       </c>
       <c r="Y3" s="1" t="s">
@@ -848,19 +974,19 @@
       <c r="AA3" s="2">
         <v>250000</v>
       </c>
-      <c r="AB3" t="s">
+      <c r="AB3" t="s" s="0">
         <v>37</v>
       </c>
-      <c r="AC3" t="s">
+      <c r="AC3" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="AD3" t="s">
+      <c r="AD3" t="s" s="0">
         <v>35</v>
       </c>
       <c r="AE3" s="2">
         <v>30</v>
       </c>
-      <c r="AF3" t="s">
+      <c r="AF3" t="s" s="0">
         <v>51</v>
       </c>
     </row>
